--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484603_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484603_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0715</v>
+        <v>4.7664</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9732</v>
+        <v>2.891</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0984</v>
+        <v>1.8754</v>
       </c>
       <c r="G2" t="n">
         <v>3.083</v>
@@ -610,13 +610,13 @@
         <v>2.7489</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.2619</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1441</v>
+        <v>0.0619</v>
       </c>
       <c r="U2" t="n">
-        <v>0.423</v>
+        <v>0.2</v>
       </c>
       <c r="V2" t="n">
         <v>0.3219</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.055</v>
+        <v>4.6765</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8548</v>
+        <v>3.2534</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2002</v>
+        <v>1.4232</v>
       </c>
       <c r="G3" t="n">
         <v>4.4931</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8046</v>
+        <v>-0.1831</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9909</v>
+        <v>-0.5924</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1863</v>
+        <v>0.4093</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6667</v>
+        <v>1.2502</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9314</v>
+        <v>1.2502</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7353</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7714</v>
+        <v>1.2502</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7104</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.061</v>
+        <v>1.2502</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8756</v>
+        <v>1.2502</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1671</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7085</v>
+        <v>1.2502</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8958</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5433</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3525</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2069</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7496</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5427999999999999</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2502</v>
+        <v>1.0155</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2502</v>
+        <v>0.3544</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.661</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2502</v>
+        <v>2.7714</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.7104</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2502</v>
+        <v>1.061</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2502</v>
+        <v>1.8756</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.1671</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2502</v>
+        <v>0.7085</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.8958</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.5433</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.3525</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0.4444</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.1727</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.6171</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="6">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2423</v>
+        <v>-0.3324</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5831</v>
+        <v>0.4047</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3408</v>
+        <v>-0.7371</v>
       </c>
       <c r="G7" t="n">
         <v>0.6808999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>0.3665</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0562</v>
+        <v>0.4815</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0746</v>
+        <v>-0.253</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1309</v>
+        <v>0.7345</v>
       </c>
       <c r="V7" t="n">
         <v>-0.945</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. PANOS HUERTAS</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7714</v>
+        <v>-1.3392</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7162</v>
+        <v>-2.6814</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9448</v>
+        <v>1.3422</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3669</v>
+        <v>-2.0221</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9122</v>
+        <v>-0.2495</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.2791</v>
+        <v>-1.7726</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5971</v>
+        <v>-1.9148</v>
       </c>
       <c r="K8" t="n">
-        <v>0.842</v>
+        <v>-0.7835</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.4391</v>
+        <v>-1.1313</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2302</v>
+        <v>-0.1072</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0701</v>
+        <v>0.5341</v>
       </c>
       <c r="O8" t="n">
-        <v>0.16</v>
+        <v>-0.6413</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1833</v>
+        <v>1.4661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0995</v>
+        <v>-0.5498</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1007</v>
+        <v>-0.7832</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0196</v>
+        <v>-0.2168</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1203</v>
+        <v>-0.5664</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>M. PANOS HUERTAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0181</v>
+        <v>-1.6336</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1622</v>
+        <v>-2.7022</v>
       </c>
       <c r="F9" t="n">
-        <v>1.144</v>
+        <v>1.0686</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0221</v>
+        <v>-1.3669</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2495</v>
+        <v>0.9122</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7726</v>
+        <v>-2.2791</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9148</v>
+        <v>-1.5971</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7835</v>
+        <v>0.842</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1313</v>
+        <v>-2.4391</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1072</v>
+        <v>0.2302</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5341</v>
+        <v>0.0701</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6413</v>
+        <v>0.16</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4661</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.5498</v>
+        <v>-1.0995</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4621</v>
+        <v>0.2385</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6976</v>
+        <v>-0.0056</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7645999999999999</v>
+        <v>0.2441</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. AVINO GOMEZ-SENENT</t>
+          <t>P. ROCATI ALEGRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0619</v>
+        <v>-1.7771</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6938</v>
+        <v>-2.7648</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6319</v>
+        <v>0.9877</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0885</v>
+        <v>-0.017</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2961</v>
+        <v>-0.6774</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3846</v>
+        <v>0.6604</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.641</v>
+        <v>-0.7754</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.8269</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.641</v>
+        <v>0.0515</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5525</v>
+        <v>0.7584</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2961</v>
+        <v>0.1495</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2564</v>
+        <v>0.6089</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6493</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>-2.1991</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3241</v>
+        <v>-0.5219</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2202</v>
+        <v>0.2097</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1039</v>
+        <v>-0.7315</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>J. AVINO GOMEZ-SENENT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4085</v>
+        <v>-2.0401</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9792</v>
+        <v>-2.5977</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4293</v>
+        <v>0.5576</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5411</v>
+        <v>-0.0885</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2204</v>
+        <v>0.2961</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3207</v>
+        <v>-0.3846</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2568</v>
+        <v>-0.641</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4492</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1925</v>
+        <v>-0.641</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2843</v>
+        <v>0.5525</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2288</v>
+        <v>0.2961</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5131</v>
+        <v>0.2564</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1991</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.2149</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0158</v>
+        <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6536</v>
+        <v>-0.3022</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2255</v>
+        <v>-0.1241</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5719</v>
+        <v>-0.1782</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ROCATI ALEGRE</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4531</v>
+        <v>-3.0073</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3417</v>
+        <v>-2.6523</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8885999999999999</v>
+        <v>-0.355</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.017</v>
+        <v>-0.5411</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6774</v>
+        <v>-0.2204</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6604</v>
+        <v>-0.3207</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7754</v>
+        <v>-0.2568</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8269</v>
+        <v>-0.4492</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0515</v>
+        <v>0.1925</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7584</v>
+        <v>-0.2843</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1495</v>
+        <v>0.2288</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6089</v>
+        <v>-0.5131</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9163</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1991</v>
+        <v>-4.2149</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2828</v>
+        <v>2.0158</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1979</v>
+        <v>0.0549</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3673</v>
+        <v>0.5524</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8306</v>
+        <v>-0.4976</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3219</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.4626</v>
+        <v>-3.9183</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9365</v>
+        <v>-2.4417</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5261</v>
+        <v>-1.4766</v>
       </c>
       <c r="G13" t="n">
         <v>-1.0122</v>
@@ -1468,13 +1468,13 @@
         <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5341</v>
+        <v>0.0102</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.276</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2366</v>
+        <v>0.2862</v>
       </c>
       <c r="V13" t="n">
         <v>-1.267</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.939699999999999</v>
+        <v>-1.389199999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.286700000000002</v>
+        <v>-6.736199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>5.347</v>
+        <v>5.347000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>8.181000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>14.6606</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7384</v>
+        <v>-1.1878</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0217</v>
+        <v>-0.4712000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7166999999999999</v>
+        <v>-0.7167000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-3.8008</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. MARCO LOPEZ</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.477</v>
+        <v>2.862</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1421</v>
+        <v>0.028</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3349</v>
+        <v>2.834</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.9019</v>
+        <v>-1.1549</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7575</v>
+        <v>-2.4723</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1444</v>
+        <v>1.3174</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5978</v>
+        <v>-0.1469</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7743</v>
+        <v>-1.6571</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1765</v>
+        <v>1.5101</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3041</v>
+        <v>-1.008</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9831</v>
+        <v>-0.8152</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.321</v>
+        <v>-0.1928</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0158</v>
+        <v>2.3823</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0995</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1154</v>
+        <v>3.4819</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0961</v>
+        <v>0.0456</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5724</v>
+        <v>-0.3144</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5236</v>
+        <v>0.3601</v>
       </c>
       <c r="V15" t="n">
-        <v>1.267</v>
+        <v>1.5889</v>
       </c>
       <c r="W15" t="n">
-        <v>1.267</v>
+        <v>1.5889</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4978</v>
+        <v>2.739</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3566</v>
+        <v>1.8172</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8544</v>
+        <v>0.9218</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1549</v>
+        <v>2.3129</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4723</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3174</v>
+        <v>1.6733</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1469</v>
+        <v>2.8123</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6571</v>
+        <v>0.7862</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5101</v>
+        <v>2.0261</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.008</v>
+        <v>-0.4994</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8152</v>
+        <v>-0.1466</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1928</v>
+        <v>-0.3528</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3823</v>
+        <v>0.733</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0995</v>
+        <v>-0.9163</v>
       </c>
       <c r="R16" t="n">
-        <v>3.4819</v>
+        <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3186</v>
+        <v>-0.3069</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.0788</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3805</v>
+        <v>-0.2281</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>H. MARCO LOPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2028</v>
+        <v>2.2007</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5288</v>
+        <v>0.0844</v>
       </c>
       <c r="F17" t="n">
-        <v>0.674</v>
+        <v>2.1163</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3129</v>
+        <v>-1.9019</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6395999999999999</v>
+        <v>-1.7575</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6733</v>
+        <v>-0.1444</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8123</v>
+        <v>-0.5978</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7862</v>
+        <v>-0.7743</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0261</v>
+        <v>0.1765</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4994</v>
+        <v>-1.3041</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1466</v>
+        <v>-0.9831</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3528</v>
+        <v>-0.321</v>
       </c>
       <c r="P17" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9163</v>
+        <v>-1.0995</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6493</v>
+        <v>3.1154</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8431</v>
+        <v>0.8198</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3673</v>
+        <v>0.5147</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4759</v>
+        <v>0.305</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.815</v>
+        <v>1.0923</v>
       </c>
       <c r="E18" t="n">
-        <v>1.178</v>
+        <v>0.5049</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6369</v>
+        <v>0.5874</v>
       </c>
       <c r="G18" t="n">
         <v>0.7907</v>
@@ -1858,13 +1858,13 @@
         <v>1.0995</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0846</v>
+        <v>0.362</v>
       </c>
       <c r="T18" t="n">
-        <v>1.08</v>
+        <v>0.4069</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0047</v>
+        <v>-0.0449</v>
       </c>
       <c r="V18" t="n">
         <v>1.5889</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4526</v>
+        <v>0.3251</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8199</v>
+        <v>0.3251</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2725</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2661</v>
+        <v>0.3251</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2854</v>
+        <v>0.3251</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0194</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4811</v>
+        <v>0.3251</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5327</v>
+        <v>0.3251</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0515</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2151</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2472</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0321</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9752999999999999</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2006</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7746</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3251</v>
+        <v>0.1554</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3251</v>
+        <v>-1.8199</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.9752</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3251</v>
+        <v>-0.2661</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3251</v>
+        <v>-0.2854</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.0194</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3251</v>
+        <v>-0.4811</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3251</v>
+        <v>-0.5327</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.2151</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.2472</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.0321</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.678</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.2006</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.4774</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1188</v>
+        <v>0.005</v>
       </c>
       <c r="E22" t="n">
         <v>0.0183</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1371</v>
+        <v>-0.0132</v>
       </c>
       <c r="G22" t="n">
         <v>0.0474</v>
@@ -2170,13 +2170,13 @@
         <v>0.1833</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0275</v>
+        <v>0.0963</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U22" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.2064</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3219</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9609</v>
+        <v>-0.628</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1065</v>
+        <v>-1.7585</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8544</v>
+        <v>1.1305</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1183</v>
+        <v>-0.9623</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6115</v>
+        <v>-0.6737</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5068</v>
+        <v>-0.2885</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.648</v>
+        <v>-1.217</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8147</v>
+        <v>-0.576</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1667</v>
+        <v>-0.641</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4703</v>
+        <v>0.2548</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7968</v>
+        <v>-0.0977</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6735</v>
+        <v>0.3525</v>
       </c>
       <c r="P23" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0158</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1991</v>
+        <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.151</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0234</v>
+        <v>0.3748</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3162</v>
+        <v>-0.2238</v>
       </c>
       <c r="V23" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.5339</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.319</v>
+        <v>-0.6576</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6758999999999999</v>
+        <v>1.0605</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.995</v>
+        <v>-1.7181</v>
       </c>
       <c r="G24" t="n">
         <v>-0.6453</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7629</v>
+        <v>-0.1014</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7345</v>
+        <v>-0.3499</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0284</v>
+        <v>0.2485</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6439</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.3783</v>
+        <v>-1.4722</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3354</v>
+        <v>-1.068</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9571</v>
+        <v>-0.4041</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9623</v>
+        <v>-3.1183</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6737</v>
+        <v>-2.6115</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2885</v>
+        <v>-0.5068</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.217</v>
+        <v>-1.648</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.576</v>
+        <v>-1.8147</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.641</v>
+        <v>0.1667</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2548</v>
+        <v>-1.4703</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0977</v>
+        <v>-0.7968</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3525</v>
+        <v>-0.6735</v>
       </c>
       <c r="P25" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R25" t="n">
-        <v>1.0995</v>
+        <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5993000000000001</v>
+        <v>0.1959</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2021</v>
+        <v>0.0619</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3972</v>
+        <v>0.134</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.5339</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.5208</v>
+        <v>-1.5709</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.8997</v>
+        <v>-2.2266</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3789</v>
+        <v>0.6558</v>
       </c>
       <c r="G26" t="n">
         <v>-2.0777</v>
@@ -2482,13 +2482,13 @@
         <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3044</v>
+        <v>0.6456</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1471</v>
+        <v>0.526</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1573</v>
+        <v>0.1195</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3219</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.483</v>
+        <v>-3.4204</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.6473</v>
+        <v>-3.2627</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1643</v>
+        <v>-0.1578</v>
       </c>
       <c r="G27" t="n">
         <v>-2.481</v>
@@ -2560,13 +2560,13 @@
         <v>2.1991</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.269</v>
+        <v>-0.2064</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.5151</v>
       </c>
       <c r="U27" t="n">
-        <v>0.6307</v>
+        <v>0.3086</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,25 +2593,25 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>1.939699999999999</v>
+        <v>2.5806</v>
       </c>
       <c r="E28" t="n">
-        <v>-5.347</v>
+        <v>-5.3471</v>
       </c>
       <c r="F28" t="n">
-        <v>7.286499999999999</v>
+        <v>7.9278</v>
       </c>
       <c r="G28" t="n">
         <v>-8.1812</v>
       </c>
       <c r="H28" t="n">
-        <v>-8.181000000000001</v>
+        <v>-8.180999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6146</v>
+        <v>-0.6145999999999996</v>
       </c>
       <c r="K28" t="n">
         <v>-3.0211</v>
@@ -2620,16 +2620,16 @@
         <v>2.4063</v>
       </c>
       <c r="M28" t="n">
-        <v>-7.5664</v>
+        <v>-7.566400000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.159899999999999</v>
+        <v>-5.1599</v>
       </c>
       <c r="O28" t="n">
         <v>-2.4065</v>
       </c>
       <c r="P28" t="n">
-        <v>4.581499999999999</v>
+        <v>4.5815</v>
       </c>
       <c r="Q28" t="n">
         <v>-14.6605</v>
@@ -2638,13 +2638,13 @@
         <v>19.242</v>
       </c>
       <c r="S28" t="n">
-        <v>1.7384</v>
+        <v>2.3795</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7165000000000002</v>
+        <v>0.7166</v>
       </c>
       <c r="U28" t="n">
-        <v>1.0217</v>
+        <v>1.6627</v>
       </c>
       <c r="V28" t="n">
         <v>3.801</v>
